--- a/docs/Pré-TPI_Journal_de_Travail_Anthony.xlsx
+++ b/docs/Pré-TPI_Journal_de_Travail_Anthony.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/pv22nbo_eduvaud_ch/Documents/Bureau/Pré-TPI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="453" documentId="13_ncr:1_{EFDCB34D-4D99-487E-82C9-6E7A8D14F32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34D557C0-FBF6-41F9-A0AA-166A4B717E69}"/>
+  <xr:revisionPtr revIDLastSave="798" documentId="13_ncr:1_{EFDCB34D-4D99-487E-82C9-6E7A8D14F32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB783560-97AB-4663-97C4-EB287DB6D0EB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="135">
   <si>
     <t>Jour</t>
   </si>
@@ -303,6 +303,147 @@
   </si>
   <si>
     <t xml:space="preserve">Création du Menu principale </t>
+  </si>
+  <si>
+    <t>Modification de la Maquette</t>
+  </si>
+  <si>
+    <t>Ajout de la page de pseudo pour la maquette</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Création du design du Menu Jouer une Partie  </t>
+  </si>
+  <si>
+    <t>Enlever les emojis pour les titres et sous titres</t>
+  </si>
+  <si>
+    <t>Problème avec les émojis mis de coté pour l'instant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Association du main_menu et du game_menu avec le bouton Jouer </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implémentation du bouton arrière du menu Jouer une Partie </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aide avec Gemini </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Création du design du menu Score et Statistiques </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changer les commentaire de francais à anglais </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Régler boutton Retour pour Score et Statistiques  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Association avec le boutton Score et Statistiques du menu </t>
+  </si>
+  <si>
+    <t>Pour Menu de Navigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Régler problème de date dans planificatin initiale  dans Gantt Project </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remettre la Planification initiale corriger </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajout de l'unicité dans le MCD pour les questions  </t>
+  </si>
+  <si>
+    <t>Documentation 13:26</t>
+  </si>
+  <si>
+    <t>Ajout de la maquette dans le Github</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Création  du design de la page de Login  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intégration login page dans le main </t>
+  </si>
+  <si>
+    <t>Création dossier assets/images</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Création du design de la Page Ajout de Question </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insertion de données dans la BD </t>
+  </si>
+  <si>
+    <t>Commencement</t>
+  </si>
+  <si>
+    <t>Not Null,Mandatory,Varchar</t>
+  </si>
+  <si>
+    <t>Modifier page login pour avoir la création d'un joueur et la connexion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modification de la Maquette </t>
+  </si>
+  <si>
+    <t>Remettre la maquette de la page de login + Remettre MLD</t>
+  </si>
+  <si>
+    <t>Fait dans le ReadMe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manuel d'Installation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Continuation du Manuel d'Installation  </t>
+  </si>
+  <si>
+    <t>Ajout des boutons se connecter et Créer un compte, Design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modification de la page login  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Création Pull Requests </t>
+  </si>
+  <si>
+    <t>feature/ui</t>
+  </si>
+  <si>
+    <t>Création Nouvelle feature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exportation en script + remodifier dans DB Browser </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modification Exportation MLD en Script </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gestion Utilisateurs pour la page login </t>
+  </si>
+  <si>
+    <t>data_persistance_management</t>
+  </si>
+  <si>
+    <t>Génération aléatoire du quiz</t>
+  </si>
+  <si>
+    <t>Continuation des insert into</t>
+  </si>
+  <si>
+    <t>Changement planification initiale, Oublie de le remettre dans la doc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insertion des thèmes  dans la BD  </t>
+  </si>
+  <si>
+    <t>Thèmes Animaux,Drapeaux et Informatique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insertion des questions  dans la BD   </t>
+  </si>
+  <si>
+    <t>Partie Réalisation</t>
   </si>
 </sst>
 </file>
@@ -370,7 +511,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -421,6 +562,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1037,25 +1181,25 @@
                   <c:v>3.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.75</c:v>
+                  <c:v>4.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.25</c:v>
+                  <c:v>12.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.75</c:v>
+                  <c:v>9.25</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2</c:v>
+                  <c:v>2.25</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.75</c:v>
+                  <c:v>3.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1756,10 +1900,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BDEB89E1-6F36-4738-9369-27FC44324FE7}" name="Tableau1" displayName="Tableau1" ref="A1:F300" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A1:F300" xr:uid="{BDEB89E1-6F36-4738-9369-27FC44324FE7}"/>
@@ -2075,7 +2215,7 @@
     <col min="2" max="2" width="13.375" style="15" customWidth="1"/>
     <col min="3" max="3" width="15.25" style="12" customWidth="1"/>
     <col min="4" max="4" width="24.75" style="5" customWidth="1"/>
-    <col min="5" max="5" width="88.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="96.25" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="82.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2939,303 +3079,709 @@
       <c r="E44" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F44" s="8"/>
+      <c r="F44" s="8" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="45" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="6"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
+      <c r="A45" s="6">
+        <v>46083</v>
+      </c>
+      <c r="B45" s="14">
+        <v>4</v>
+      </c>
+      <c r="C45" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="46" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="6"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
+      <c r="A46" s="6">
+        <v>46083</v>
+      </c>
+      <c r="B46" s="14">
+        <v>4</v>
+      </c>
+      <c r="C46" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="47" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="6"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
+      <c r="A47" s="6">
+        <v>46083</v>
+      </c>
+      <c r="B47" s="14">
+        <v>4</v>
+      </c>
+      <c r="C47" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="48" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="6"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="8"/>
+      <c r="A48" s="6">
+        <v>46083</v>
+      </c>
+      <c r="B48" s="14">
+        <v>4</v>
+      </c>
+      <c r="C48" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>94</v>
+      </c>
       <c r="F48" s="8"/>
     </row>
     <row r="49" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="6"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="8"/>
+      <c r="A49" s="6">
+        <v>46083</v>
+      </c>
+      <c r="B49" s="14">
+        <v>4</v>
+      </c>
+      <c r="C49" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>93</v>
+      </c>
       <c r="F49" s="8"/>
     </row>
     <row r="50" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="6"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="8"/>
+      <c r="A50" s="6">
+        <v>46083</v>
+      </c>
+      <c r="B50" s="14">
+        <v>4</v>
+      </c>
+      <c r="C50" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>96</v>
+      </c>
       <c r="F50" s="8"/>
     </row>
     <row r="51" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="6"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="8"/>
+      <c r="A51" s="6">
+        <v>46084</v>
+      </c>
+      <c r="B51" s="14">
+        <v>4</v>
+      </c>
+      <c r="C51" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>97</v>
+      </c>
       <c r="F51" s="8"/>
     </row>
     <row r="52" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="6"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="8"/>
+      <c r="A52" s="6">
+        <v>46084</v>
+      </c>
+      <c r="B52" s="14">
+        <v>4</v>
+      </c>
+      <c r="C52" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="F52" s="8"/>
     </row>
     <row r="53" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="6"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="8"/>
+      <c r="A53" s="6">
+        <v>46084</v>
+      </c>
+      <c r="B53" s="14">
+        <v>4</v>
+      </c>
+      <c r="C53" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>99</v>
+      </c>
       <c r="F53" s="8"/>
     </row>
     <row r="54" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="6"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
+      <c r="A54" s="6">
+        <v>46084</v>
+      </c>
+      <c r="B54" s="14">
+        <v>4</v>
+      </c>
+      <c r="C54" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="55" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="6"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="8"/>
+      <c r="A55" s="6">
+        <v>46084</v>
+      </c>
+      <c r="B55" s="14">
+        <v>4</v>
+      </c>
+      <c r="C55" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>102</v>
+      </c>
       <c r="F55" s="8"/>
     </row>
     <row r="56" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="6"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="11"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="8"/>
+      <c r="A56" s="6">
+        <v>46084</v>
+      </c>
+      <c r="B56" s="14">
+        <v>4</v>
+      </c>
+      <c r="C56" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="F56" s="8"/>
     </row>
     <row r="57" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="6"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="8"/>
+      <c r="A57" s="6">
+        <v>46084</v>
+      </c>
+      <c r="B57" s="14">
+        <v>4</v>
+      </c>
+      <c r="C57" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>103</v>
+      </c>
       <c r="F57" s="8"/>
     </row>
     <row r="58" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="6"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="11"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="8"/>
+      <c r="A58" s="6">
+        <v>46084</v>
+      </c>
+      <c r="B58" s="14">
+        <v>4</v>
+      </c>
+      <c r="C58" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>104</v>
+      </c>
       <c r="F58" s="8"/>
     </row>
     <row r="59" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="6"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="8"/>
+      <c r="A59" s="6">
+        <v>46084</v>
+      </c>
+      <c r="B59" s="14">
+        <v>4</v>
+      </c>
+      <c r="C59" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>105</v>
+      </c>
       <c r="F59" s="8"/>
     </row>
     <row r="60" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="6"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="11"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="8"/>
+      <c r="A60" s="6">
+        <v>46084</v>
+      </c>
+      <c r="B60" s="14">
+        <v>4</v>
+      </c>
+      <c r="C60" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>106</v>
+      </c>
       <c r="F60" s="8"/>
     </row>
     <row r="61" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="6"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="11"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="8"/>
+      <c r="A61" s="6">
+        <v>46084</v>
+      </c>
+      <c r="B61" s="14">
+        <v>4</v>
+      </c>
+      <c r="C61" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>107</v>
+      </c>
       <c r="F61" s="8"/>
     </row>
     <row r="62" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="6"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="11"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="8"/>
+      <c r="A62" s="6">
+        <v>46085</v>
+      </c>
+      <c r="B62" s="14">
+        <v>4</v>
+      </c>
+      <c r="C62" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>109</v>
+      </c>
       <c r="F62" s="8"/>
     </row>
     <row r="63" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="6"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="11"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="8"/>
+      <c r="A63" s="6">
+        <v>46085</v>
+      </c>
+      <c r="B63" s="14">
+        <v>4</v>
+      </c>
+      <c r="C63" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>108</v>
+      </c>
       <c r="F63" s="8"/>
     </row>
     <row r="64" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="6"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="11"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
+      <c r="A64" s="6">
+        <v>46090</v>
+      </c>
+      <c r="B64" s="14">
+        <v>5</v>
+      </c>
+      <c r="C64" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="65" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="6"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="11"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
+      <c r="A65" s="6">
+        <v>46090</v>
+      </c>
+      <c r="B65" s="14">
+        <v>5</v>
+      </c>
+      <c r="C65" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="66" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="6"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="11"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
+      <c r="A66" s="6">
+        <v>46090</v>
+      </c>
+      <c r="B66" s="14">
+        <v>5</v>
+      </c>
+      <c r="C66" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="67" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="6"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="11"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="8"/>
+      <c r="A67" s="6">
+        <v>46090</v>
+      </c>
+      <c r="B67" s="14">
+        <v>5</v>
+      </c>
+      <c r="C67" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="68" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="6"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="11"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
+      <c r="A68" s="6">
+        <v>46090</v>
+      </c>
+      <c r="B68" s="14">
+        <v>5</v>
+      </c>
+      <c r="C68" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="69" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="6"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="11"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="8"/>
+      <c r="A69" s="6">
+        <v>46091</v>
+      </c>
+      <c r="B69" s="14">
+        <v>5</v>
+      </c>
+      <c r="C69" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>118</v>
+      </c>
       <c r="F69" s="8"/>
     </row>
     <row r="70" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="6"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="11"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
+      <c r="A70" s="6">
+        <v>46091</v>
+      </c>
+      <c r="B70" s="14">
+        <v>5</v>
+      </c>
+      <c r="C70" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="71" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="6"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="11"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
+      <c r="A71" s="6">
+        <v>46091</v>
+      </c>
+      <c r="B71" s="14">
+        <v>5</v>
+      </c>
+      <c r="C71" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="6"/>
-      <c r="B72" s="14"/>
-      <c r="C72" s="11"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
+      <c r="A72" s="6">
+        <v>46091</v>
+      </c>
+      <c r="B72" s="14">
+        <v>5</v>
+      </c>
+      <c r="C72" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="73" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="6"/>
-      <c r="B73" s="14"/>
-      <c r="C73" s="11"/>
-      <c r="D73" s="7"/>
-      <c r="E73" s="8"/>
+      <c r="A73" s="6">
+        <v>46091</v>
+      </c>
+      <c r="B73" s="14">
+        <v>5</v>
+      </c>
+      <c r="C73" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>126</v>
+      </c>
       <c r="F73" s="8"/>
     </row>
     <row r="74" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="6"/>
-      <c r="B74" s="14"/>
-      <c r="C74" s="11"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
+      <c r="A74" s="6">
+        <v>46091</v>
+      </c>
+      <c r="B74" s="14">
+        <v>5</v>
+      </c>
+      <c r="C74" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="75" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="6"/>
-      <c r="B75" s="14"/>
-      <c r="C75" s="11"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="8"/>
+      <c r="A75" s="6">
+        <v>46091</v>
+      </c>
+      <c r="B75" s="14">
+        <v>5</v>
+      </c>
+      <c r="C75" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>66</v>
+      </c>
       <c r="F75" s="8"/>
     </row>
     <row r="76" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="6"/>
-      <c r="B76" s="14"/>
-      <c r="C76" s="11"/>
-      <c r="D76" s="7"/>
-      <c r="E76" s="8"/>
+      <c r="A76" s="6">
+        <v>46091</v>
+      </c>
+      <c r="B76" s="14">
+        <v>5</v>
+      </c>
+      <c r="C76" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>123</v>
+      </c>
       <c r="F76" s="8"/>
     </row>
     <row r="77" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="6"/>
-      <c r="B77" s="14"/>
-      <c r="C77" s="11"/>
-      <c r="D77" s="7"/>
-      <c r="E77" s="8"/>
+      <c r="A77" s="6">
+        <v>46091</v>
+      </c>
+      <c r="B77" s="14">
+        <v>5</v>
+      </c>
+      <c r="C77" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>128</v>
+      </c>
       <c r="F77" s="8"/>
     </row>
     <row r="78" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="6"/>
-      <c r="B78" s="14"/>
-      <c r="C78" s="11"/>
-      <c r="D78" s="7"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
+      <c r="A78" s="6">
+        <v>46091</v>
+      </c>
+      <c r="B78" s="14">
+        <v>5</v>
+      </c>
+      <c r="C78" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="79" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="6"/>
-      <c r="B79" s="14"/>
-      <c r="C79" s="11"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
+      <c r="A79" s="6">
+        <v>46092</v>
+      </c>
+      <c r="B79" s="14">
+        <v>5</v>
+      </c>
+      <c r="C79" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="80" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="6"/>
-      <c r="B80" s="14"/>
-      <c r="C80" s="11"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="8"/>
+      <c r="A80" s="6">
+        <v>46092</v>
+      </c>
+      <c r="B80" s="14">
+        <v>5</v>
+      </c>
+      <c r="C80" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="81" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="6"/>
-      <c r="B81" s="14"/>
-      <c r="C81" s="11"/>
-      <c r="D81" s="7"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="8"/>
+      <c r="A81" s="6">
+        <v>46092</v>
+      </c>
+      <c r="B81" s="14">
+        <v>5</v>
+      </c>
+      <c r="C81" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="82" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
@@ -6659,7 +7205,7 @@
       </c>
       <c r="B3" s="11">
         <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6668,7 +7214,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>1.25</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6686,7 +7232,7 @@
       </c>
       <c r="B6" s="11">
         <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>6.75</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6695,7 +7241,7 @@
       </c>
       <c r="B7" s="11">
         <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>2</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -6713,7 +7259,7 @@
       </c>
       <c r="B9" s="11">
         <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/docs/Pré-TPI_Journal_de_Travail_Anthony.xlsx
+++ b/docs/Pré-TPI_Journal_de_Travail_Anthony.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/pv22nbo_eduvaud_ch/Documents/Bureau/Pré-TPI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="798" documentId="13_ncr:1_{EFDCB34D-4D99-487E-82C9-6E7A8D14F32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB783560-97AB-4663-97C4-EB287DB6D0EB}"/>
+  <xr:revisionPtr revIDLastSave="1066" documentId="13_ncr:1_{EFDCB34D-4D99-487E-82C9-6E7A8D14F32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F82D1296-918D-4C9F-BCAA-74877AEBBEB7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="176">
   <si>
     <t>Jour</t>
   </si>
@@ -353,9 +353,6 @@
     <t xml:space="preserve">Ajout de l'unicité dans le MCD pour les questions  </t>
   </si>
   <si>
-    <t>Documentation 13:26</t>
-  </si>
-  <si>
     <t>Ajout de la maquette dans le Github</t>
   </si>
   <si>
@@ -444,6 +441,132 @@
   </si>
   <si>
     <t>Partie Réalisation</t>
+  </si>
+  <si>
+    <t>Création des sous-dossier par thèmes</t>
+  </si>
+  <si>
+    <t>Animaux,Drapeaux et Informatique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modification insertions des questions dans la BD </t>
+  </si>
+  <si>
+    <t>Animaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insertion des réponses dans la BD </t>
+  </si>
+  <si>
+    <t>random_quiz_generation</t>
+  </si>
+  <si>
+    <t>Gestion du temps et des réponses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Résolution problème login page </t>
+  </si>
+  <si>
+    <t>game_quiz.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continuaton Gestion du temps et des réponses  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interface Question et réponses  </t>
+  </si>
+  <si>
+    <t>Quand je choisis Animal, il y a des questions des autres thèmes</t>
+  </si>
+  <si>
+    <t>Problème Questions</t>
+  </si>
+  <si>
+    <t>Quand je clique sur facile, il y a des questions moyen ou difficile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Problème Choix difficulté </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insertion des images dans le dossier animals </t>
+  </si>
+  <si>
+    <t>Image en double ou pas d'image qui s'affichait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Problème Affichage image dans le jeu </t>
+  </si>
+  <si>
+    <t>Problème avec le boutton créer un compte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Problème de Database is locked </t>
+  </si>
+  <si>
+    <t>Drapeau + Informatique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insertion des réponses dans la BD   </t>
+  </si>
+  <si>
+    <t>Partie Tests</t>
+  </si>
+  <si>
+    <t>Dans les dossier Drapeaux et Informatique, Pas Fini</t>
+  </si>
+  <si>
+    <t>Insertion des images dans le dossier Drapeaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continuation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insertion des images dans le dossier Drapeaux </t>
+  </si>
+  <si>
+    <t>Ajout dans partie Historique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réglage du timer  </t>
+  </si>
+  <si>
+    <t>quiz_engine.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mettre les paramètres de sortie et d'entrée en commentaires </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajout des entetes de fichiers </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajout des entetes de fichiers  </t>
+  </si>
+  <si>
+    <t>Continuation et finalisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changement image code  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score et Statistiques </t>
+  </si>
+  <si>
+    <t>Partie Jouées,Score moyen et Temps moyen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finalisation </t>
+  </si>
+  <si>
+    <t>Modification du README</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Documentation  </t>
+  </si>
+  <si>
+    <t>9.1 + Glossaire et Table d'illustration</t>
+  </si>
+  <si>
+    <t>Rendu Finale Par mail</t>
   </si>
 </sst>
 </file>
@@ -1184,22 +1307,22 @@
                   <c:v>4.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12.75</c:v>
+                  <c:v>21.25</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.25</c:v>
+                  <c:v>14.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.25</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.25</c:v>
+                  <c:v>7.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1900,6 +2023,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BDEB89E1-6F36-4738-9369-27FC44324FE7}" name="Tableau1" displayName="Tableau1" ref="A1:F300" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A1:F300" xr:uid="{BDEB89E1-6F36-4738-9369-27FC44324FE7}"/>
@@ -3339,7 +3466,7 @@
         <v>11</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="F58" s="8"/>
     </row>
@@ -3357,7 +3484,7 @@
         <v>9</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F59" s="8"/>
     </row>
@@ -3375,7 +3502,7 @@
         <v>9</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F60" s="8"/>
     </row>
@@ -3393,7 +3520,7 @@
         <v>9</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F61" s="8"/>
     </row>
@@ -3411,7 +3538,7 @@
         <v>9</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F62" s="8"/>
     </row>
@@ -3429,7 +3556,7 @@
         <v>9</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F63" s="8"/>
     </row>
@@ -3447,10 +3574,10 @@
         <v>9</v>
       </c>
       <c r="E64" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F64" s="8" t="s">
         <v>110</v>
-      </c>
-      <c r="F64" s="8" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3470,7 +3597,7 @@
         <v>80</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3487,10 +3614,10 @@
         <v>8</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3510,7 +3637,7 @@
         <v>72</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3527,10 +3654,10 @@
         <v>13</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3547,7 +3674,7 @@
         <v>13</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F69" s="8"/>
     </row>
@@ -3565,10 +3692,10 @@
         <v>9</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3585,10 +3712,10 @@
         <v>13</v>
       </c>
       <c r="E71" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F71" s="8" t="s">
         <v>121</v>
-      </c>
-      <c r="F71" s="8" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3605,10 +3732,10 @@
         <v>13</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3625,7 +3752,7 @@
         <v>9</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F73" s="8"/>
     </row>
@@ -3643,10 +3770,10 @@
         <v>9</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3681,7 +3808,7 @@
         <v>13</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F76" s="8"/>
     </row>
@@ -3699,7 +3826,7 @@
         <v>9</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F77" s="8"/>
     </row>
@@ -3717,10 +3844,10 @@
         <v>9</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3740,7 +3867,7 @@
         <v>72</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3757,10 +3884,10 @@
         <v>9</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3780,255 +3907,602 @@
         <v>72</v>
       </c>
       <c r="F81" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="6">
+        <v>46097</v>
+      </c>
+      <c r="B82" s="14">
+        <v>6</v>
+      </c>
+      <c r="C82" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E82" s="8" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="6"/>
-      <c r="B82" s="14"/>
-      <c r="C82" s="11"/>
-      <c r="D82" s="7"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
+      <c r="F82" s="8" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="83" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="6"/>
-      <c r="B83" s="14"/>
-      <c r="C83" s="11"/>
-      <c r="D83" s="7"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="8"/>
+      <c r="A83" s="6">
+        <v>46097</v>
+      </c>
+      <c r="B83" s="14">
+        <v>6</v>
+      </c>
+      <c r="C83" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="84" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="6"/>
-      <c r="B84" s="14"/>
-      <c r="C84" s="11"/>
-      <c r="D84" s="7"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="8"/>
+      <c r="A84" s="6">
+        <v>46097</v>
+      </c>
+      <c r="B84" s="14">
+        <v>6</v>
+      </c>
+      <c r="C84" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="85" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="6"/>
-      <c r="B85" s="14"/>
-      <c r="C85" s="11"/>
-      <c r="D85" s="7"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="8"/>
+      <c r="A85" s="6">
+        <v>46097</v>
+      </c>
+      <c r="B85" s="14">
+        <v>6</v>
+      </c>
+      <c r="C85" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="86" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="6"/>
-      <c r="B86" s="14"/>
-      <c r="C86" s="11"/>
-      <c r="D86" s="7"/>
-      <c r="E86" s="8"/>
+      <c r="A86" s="6">
+        <v>46097</v>
+      </c>
+      <c r="B86" s="14">
+        <v>6</v>
+      </c>
+      <c r="C86" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>122</v>
+      </c>
       <c r="F86" s="8"/>
     </row>
     <row r="87" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="6"/>
-      <c r="B87" s="14"/>
-      <c r="C87" s="11"/>
-      <c r="D87" s="7"/>
-      <c r="E87" s="8"/>
+      <c r="A87" s="6">
+        <v>46097</v>
+      </c>
+      <c r="B87" s="14">
+        <v>6</v>
+      </c>
+      <c r="C87" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>140</v>
+      </c>
       <c r="F87" s="8"/>
     </row>
     <row r="88" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="6"/>
-      <c r="B88" s="14"/>
-      <c r="C88" s="11"/>
-      <c r="D88" s="7"/>
-      <c r="E88" s="8"/>
+      <c r="A88" s="6">
+        <v>46097</v>
+      </c>
+      <c r="B88" s="14">
+        <v>6</v>
+      </c>
+      <c r="C88" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>141</v>
+      </c>
       <c r="F88" s="8"/>
     </row>
     <row r="89" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="6"/>
-      <c r="B89" s="14"/>
-      <c r="C89" s="11"/>
-      <c r="D89" s="7"/>
-      <c r="E89" s="8"/>
-      <c r="F89" s="8"/>
+      <c r="A89" s="6">
+        <v>46098</v>
+      </c>
+      <c r="B89" s="14">
+        <v>6</v>
+      </c>
+      <c r="C89" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="90" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="6"/>
-      <c r="B90" s="14"/>
-      <c r="C90" s="11"/>
-      <c r="D90" s="7"/>
-      <c r="E90" s="8"/>
-      <c r="F90" s="8"/>
+      <c r="A90" s="6">
+        <v>46098</v>
+      </c>
+      <c r="B90" s="14">
+        <v>6</v>
+      </c>
+      <c r="C90" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="91" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="6"/>
-      <c r="B91" s="14"/>
-      <c r="C91" s="11"/>
-      <c r="D91" s="7"/>
-      <c r="E91" s="8"/>
-      <c r="F91" s="8"/>
+      <c r="A91" s="6">
+        <v>46098</v>
+      </c>
+      <c r="B91" s="14">
+        <v>6</v>
+      </c>
+      <c r="C91" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="92" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="6"/>
-      <c r="B92" s="14"/>
-      <c r="C92" s="11"/>
-      <c r="D92" s="7"/>
-      <c r="E92" s="8"/>
-      <c r="F92" s="8"/>
+      <c r="A92" s="6">
+        <v>46098</v>
+      </c>
+      <c r="B92" s="14">
+        <v>6</v>
+      </c>
+      <c r="C92" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="93" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="6"/>
-      <c r="B93" s="14"/>
-      <c r="C93" s="11"/>
-      <c r="D93" s="7"/>
-      <c r="E93" s="8"/>
+      <c r="A93" s="6">
+        <v>46098</v>
+      </c>
+      <c r="B93" s="14">
+        <v>6</v>
+      </c>
+      <c r="C93" s="11">
+        <v>1</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>149</v>
+      </c>
       <c r="F93" s="8"/>
     </row>
     <row r="94" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="6"/>
-      <c r="B94" s="14"/>
-      <c r="C94" s="11"/>
-      <c r="D94" s="7"/>
-      <c r="E94" s="8"/>
-      <c r="F94" s="8"/>
+      <c r="A94" s="6">
+        <v>46098</v>
+      </c>
+      <c r="B94" s="14">
+        <v>6</v>
+      </c>
+      <c r="C94" s="11">
+        <v>1.25</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="95" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="6"/>
-      <c r="B95" s="14"/>
-      <c r="C95" s="11"/>
-      <c r="D95" s="7"/>
-      <c r="E95" s="8"/>
-      <c r="F95" s="8"/>
+      <c r="A95" s="6">
+        <v>46098</v>
+      </c>
+      <c r="B95" s="14">
+        <v>6</v>
+      </c>
+      <c r="C95" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="96" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="6"/>
-      <c r="B96" s="14"/>
-      <c r="C96" s="11"/>
-      <c r="D96" s="7"/>
-      <c r="E96" s="8"/>
-      <c r="F96" s="8"/>
+      <c r="A96" s="6">
+        <v>46099</v>
+      </c>
+      <c r="B96" s="14">
+        <v>6</v>
+      </c>
+      <c r="C96" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="97" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="6"/>
-      <c r="B97" s="14"/>
-      <c r="C97" s="11"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="8"/>
-      <c r="F97" s="8"/>
+      <c r="A97" s="6">
+        <v>46099</v>
+      </c>
+      <c r="B97" s="14">
+        <v>6</v>
+      </c>
+      <c r="C97" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="98" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="6"/>
-      <c r="B98" s="14"/>
-      <c r="C98" s="11"/>
-      <c r="D98" s="7"/>
-      <c r="E98" s="8"/>
-      <c r="F98" s="8"/>
+      <c r="A98" s="6">
+        <v>46099</v>
+      </c>
+      <c r="B98" s="14">
+        <v>6</v>
+      </c>
+      <c r="C98" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="99" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="6"/>
-      <c r="B99" s="14"/>
-      <c r="C99" s="11"/>
-      <c r="D99" s="7"/>
-      <c r="E99" s="8"/>
-      <c r="F99" s="8"/>
+      <c r="A99" s="6">
+        <v>46104</v>
+      </c>
+      <c r="B99" s="14">
+        <v>7</v>
+      </c>
+      <c r="C99" s="11">
+        <v>1.25</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="100" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="6"/>
-      <c r="B100" s="14"/>
-      <c r="C100" s="11"/>
-      <c r="D100" s="7"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="8"/>
+      <c r="A100" s="6">
+        <v>46104</v>
+      </c>
+      <c r="B100" s="14">
+        <v>7</v>
+      </c>
+      <c r="C100" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="101" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="6"/>
-      <c r="B101" s="14"/>
-      <c r="C101" s="11"/>
-      <c r="D101" s="7"/>
-      <c r="E101" s="8"/>
+      <c r="A101" s="6">
+        <v>46104</v>
+      </c>
+      <c r="B101" s="14">
+        <v>7</v>
+      </c>
+      <c r="C101" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>162</v>
+      </c>
       <c r="F101" s="8"/>
     </row>
     <row r="102" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="6"/>
-      <c r="B102" s="14"/>
-      <c r="C102" s="11"/>
-      <c r="D102" s="7"/>
-      <c r="E102" s="8"/>
-      <c r="F102" s="8"/>
+      <c r="A102" s="6">
+        <v>46104</v>
+      </c>
+      <c r="B102" s="14">
+        <v>7</v>
+      </c>
+      <c r="C102" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="103" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="6"/>
-      <c r="B103" s="14"/>
-      <c r="C103" s="11"/>
-      <c r="D103" s="7"/>
-      <c r="E103" s="8"/>
+      <c r="A103" s="6">
+        <v>46104</v>
+      </c>
+      <c r="B103" s="14">
+        <v>7</v>
+      </c>
+      <c r="C103" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>165</v>
+      </c>
       <c r="F103" s="8"/>
     </row>
     <row r="104" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="6"/>
-      <c r="B104" s="14"/>
-      <c r="C104" s="11"/>
-      <c r="D104" s="7"/>
-      <c r="E104" s="8"/>
-      <c r="F104" s="8"/>
+      <c r="A104" s="6">
+        <v>46105</v>
+      </c>
+      <c r="B104" s="14">
+        <v>7</v>
+      </c>
+      <c r="C104" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="105" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="6"/>
-      <c r="B105" s="14"/>
-      <c r="C105" s="11"/>
-      <c r="D105" s="7"/>
-      <c r="E105" s="8"/>
+      <c r="A105" s="6">
+        <v>46105</v>
+      </c>
+      <c r="B105" s="14">
+        <v>7</v>
+      </c>
+      <c r="C105" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="F105" s="8"/>
     </row>
     <row r="106" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="6"/>
-      <c r="B106" s="14"/>
-      <c r="C106" s="11"/>
-      <c r="D106" s="7"/>
-      <c r="E106" s="8"/>
+      <c r="A106" s="6">
+        <v>46105</v>
+      </c>
+      <c r="B106" s="14">
+        <v>7</v>
+      </c>
+      <c r="C106" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>120</v>
+      </c>
       <c r="F106" s="8"/>
     </row>
     <row r="107" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="6"/>
-      <c r="B107" s="14"/>
-      <c r="C107" s="11"/>
-      <c r="D107" s="7"/>
-      <c r="E107" s="8"/>
-      <c r="F107" s="8"/>
+      <c r="A107" s="6">
+        <v>46105</v>
+      </c>
+      <c r="B107" s="14">
+        <v>7</v>
+      </c>
+      <c r="C107" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="108" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="6"/>
-      <c r="B108" s="14"/>
-      <c r="C108" s="11"/>
-      <c r="D108" s="7"/>
-      <c r="E108" s="8"/>
-      <c r="F108" s="8"/>
+      <c r="A108" s="6">
+        <v>46105</v>
+      </c>
+      <c r="B108" s="14">
+        <v>7</v>
+      </c>
+      <c r="C108" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="109" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="6"/>
-      <c r="B109" s="14"/>
-      <c r="C109" s="11"/>
-      <c r="D109" s="7"/>
-      <c r="E109" s="8"/>
+      <c r="A109" s="6">
+        <v>46105</v>
+      </c>
+      <c r="B109" s="14">
+        <v>7</v>
+      </c>
+      <c r="C109" s="11">
+        <v>3</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E109" s="8" t="s">
+        <v>173</v>
+      </c>
       <c r="F109" s="8"/>
     </row>
     <row r="110" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="6"/>
-      <c r="B110" s="14"/>
-      <c r="C110" s="11"/>
-      <c r="D110" s="7"/>
-      <c r="E110" s="8"/>
+      <c r="A110" s="6">
+        <v>46105</v>
+      </c>
+      <c r="B110" s="14">
+        <v>7</v>
+      </c>
+      <c r="C110" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E110" s="8" t="s">
+        <v>172</v>
+      </c>
       <c r="F110" s="8"/>
     </row>
     <row r="111" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="6"/>
-      <c r="B111" s="14"/>
-      <c r="C111" s="11"/>
-      <c r="D111" s="7"/>
-      <c r="E111" s="8"/>
-      <c r="F111" s="8"/>
+      <c r="A111" s="6">
+        <v>46106</v>
+      </c>
+      <c r="B111" s="14">
+        <v>7</v>
+      </c>
+      <c r="C111" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="112" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="6"/>
-      <c r="B112" s="14"/>
-      <c r="C112" s="11"/>
-      <c r="D112" s="7"/>
-      <c r="E112" s="8"/>
+      <c r="A112" s="6">
+        <v>46106</v>
+      </c>
+      <c r="B112" s="14">
+        <v>7</v>
+      </c>
+      <c r="C112" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E112" s="8" t="s">
+        <v>175</v>
+      </c>
       <c r="F112" s="8"/>
     </row>
     <row r="113" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -7214,7 +7688,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>12.75</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -7232,7 +7706,7 @@
       </c>
       <c r="B6" s="11">
         <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>9.25</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -7241,7 +7715,7 @@
       </c>
       <c r="B7" s="11">
         <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -7259,7 +7733,7 @@
       </c>
       <c r="B9" s="11">
         <f>SUMIF(Journal!$D$2:$D$160,Tableau13[[#This Row],[Type]],Journal!$C$2:$C$160)</f>
-        <v>3.25</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="24.95" customHeight="1" x14ac:dyDescent="0.3">
